--- a/data.mn/public/datasets/nso-medical-personnel-by-type.xlsx
+++ b/data.mn/public/datasets/nso-medical-personnel-by-type.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,8 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -424,12 +430,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>Nurses</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>personnel</t>
+          <t>Physicians</t>
         </is>
       </c>
     </row>
@@ -437,10 +443,8 @@
       <c r="A2" t="n">
         <v>2015</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+      <c r="B2" t="n">
+        <v>11357</v>
       </c>
       <c r="C2" t="n">
         <v>9563</v>
@@ -448,275 +452,269 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
+        <v>2016</v>
+      </c>
+      <c r="B3" t="n">
+        <v>11486</v>
       </c>
       <c r="C3" t="n">
-        <v>11357</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+        <v>2017</v>
+      </c>
+      <c r="B4" t="n">
+        <v>11939</v>
       </c>
       <c r="C4" t="n">
-        <v>10000</v>
+        <v>10576</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12344</v>
       </c>
       <c r="C5" t="n">
-        <v>11486</v>
+        <v>11169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+        <v>2019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12773</v>
       </c>
       <c r="C6" t="n">
-        <v>10576</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
+        <v>2020</v>
+      </c>
+      <c r="B7" t="n">
+        <v>13112</v>
       </c>
       <c r="C7" t="n">
-        <v>11939</v>
+        <v>12431</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+        <v>2021</v>
+      </c>
+      <c r="B8" t="n">
+        <v>13473</v>
       </c>
       <c r="C8" t="n">
-        <v>11169</v>
+        <v>12970</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
+        <v>2022</v>
+      </c>
+      <c r="B9" t="n">
+        <v>13947</v>
       </c>
       <c r="C9" t="n">
-        <v>12344</v>
+        <v>13983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+        <v>2023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>14494</v>
       </c>
       <c r="C10" t="n">
-        <v>11788</v>
+        <v>14978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
+        <v>2024</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15152</v>
       </c>
       <c r="C11" t="n">
-        <v>12773</v>
+        <v>15973</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>15099</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16093</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Сувилагч</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Эмч</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B2" t="n">
+        <v>11357</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9563</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B3" t="n">
+        <v>11486</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B4" t="n">
+        <v>11939</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10576</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12344</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11169</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>12773</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11788</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2020</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
+      <c r="B7" t="n">
+        <v>13112</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12431</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="n">
+        <v>13473</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12970</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B9" t="n">
+        <v>13947</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13983</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" t="n">
+        <v>14494</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14978</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15152</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15973</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>15099</v>
       </c>
       <c r="C12" t="n">
-        <v>12431</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>13112</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>12970</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>13473</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>13983</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>13947</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>14978</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14494</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>15973</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>15152</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Physicians</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
         <v>16093</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Nurses</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>15099</v>
       </c>
     </row>
   </sheetData>
